--- a/data/trans_orig/P15E_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,97 +2215,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14233</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64726</t>
+          <t>64833</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88709</t>
+          <t>88323</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19069</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53627</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>70528</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89295</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74045</t>
+          <t>81785</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88323</t>
+          <t>96701</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
